--- a/data/measures-of-position--exam_scores.xlsx
+++ b/data/measures-of-position--exam_scores.xlsx
@@ -6562,7 +6562,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Percentile rank answers: what fraction of students scored below a given value?</t>
+          <t>Percentile rank answers: what fraction of students scored at or below a given value?</t>
         </is>
       </c>
     </row>
